--- a/Docs/Communication Plan.xlsx
+++ b/Docs/Communication Plan.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d0d25a1f11c8555b/Desktop/SpaceLandMapper Docs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="13_ncr:1_{59A92193-4858-254A-AC4A-6E4AE052CB36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BF1CE4DF-2FC8-4EB0-86A6-B0DBA07D3F5C}"/>
+  <xr:revisionPtr revIDLastSave="4" documentId="13_ncr:1_{59A92193-4858-254A-AC4A-6E4AE052CB36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C7CA1F4D-922C-477E-983F-4063729CDCA6}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -690,14 +690,14 @@
     <xf numFmtId="0" fontId="8" fillId="6" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -719,6 +719,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1020,28 +1024,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A1" s="18" t="s">
+      <c r="A1" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="B1" s="15"/>
-      <c r="C1" s="15"/>
-      <c r="D1" s="15"/>
-      <c r="E1" s="15"/>
-      <c r="F1" s="15"/>
-      <c r="G1" s="15"/>
-      <c r="H1" s="15"/>
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
+      <c r="F1" s="16"/>
+      <c r="G1" s="16"/>
+      <c r="H1" s="16"/>
     </row>
     <row r="2" spans="1:8" ht="22.05" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A2" s="19" t="s">
         <v>154</v>
       </c>
-      <c r="B2" s="15"/>
-      <c r="C2" s="15"/>
-      <c r="D2" s="15"/>
-      <c r="E2" s="15"/>
-      <c r="F2" s="15"/>
-      <c r="G2" s="15"/>
-      <c r="H2" s="15"/>
+      <c r="B2" s="16"/>
+      <c r="C2" s="16"/>
+      <c r="D2" s="16"/>
+      <c r="E2" s="16"/>
+      <c r="F2" s="16"/>
+      <c r="G2" s="16"/>
+      <c r="H2" s="16"/>
     </row>
     <row r="3" spans="1:8" ht="32.549999999999997" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A3" s="6" t="s">
@@ -1050,12 +1054,12 @@
       <c r="B3" s="17" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="15"/>
-      <c r="D3" s="15"/>
-      <c r="E3" s="15"/>
-      <c r="F3" s="15"/>
-      <c r="G3" s="15"/>
-      <c r="H3" s="15"/>
+      <c r="C3" s="16"/>
+      <c r="D3" s="16"/>
+      <c r="E3" s="16"/>
+      <c r="F3" s="16"/>
+      <c r="G3" s="16"/>
+      <c r="H3" s="16"/>
     </row>
     <row r="4" spans="1:8" ht="32.549999999999997" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A4" s="6" t="s">
@@ -1064,12 +1068,12 @@
       <c r="B4" s="17" t="s">
         <v>9</v>
       </c>
-      <c r="C4" s="15"/>
-      <c r="D4" s="15"/>
-      <c r="E4" s="15"/>
-      <c r="F4" s="15"/>
-      <c r="G4" s="15"/>
-      <c r="H4" s="15"/>
+      <c r="C4" s="16"/>
+      <c r="D4" s="16"/>
+      <c r="E4" s="16"/>
+      <c r="F4" s="16"/>
+      <c r="G4" s="16"/>
+      <c r="H4" s="16"/>
     </row>
     <row r="5" spans="1:8" ht="32.549999999999997" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A5" s="6" t="s">
@@ -1078,12 +1082,12 @@
       <c r="B5" s="17" t="s">
         <v>11</v>
       </c>
-      <c r="C5" s="15"/>
-      <c r="D5" s="15"/>
-      <c r="E5" s="15"/>
-      <c r="F5" s="15"/>
-      <c r="G5" s="15"/>
-      <c r="H5" s="15"/>
+      <c r="C5" s="16"/>
+      <c r="D5" s="16"/>
+      <c r="E5" s="16"/>
+      <c r="F5" s="16"/>
+      <c r="G5" s="16"/>
+      <c r="H5" s="16"/>
     </row>
     <row r="6" spans="1:8" ht="32.549999999999997" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A6" s="6" t="s">
@@ -1092,24 +1096,24 @@
       <c r="B6" s="17" t="s">
         <v>13</v>
       </c>
-      <c r="C6" s="15"/>
-      <c r="D6" s="15"/>
-      <c r="E6" s="15"/>
-      <c r="F6" s="15"/>
-      <c r="G6" s="15"/>
-      <c r="H6" s="15"/>
+      <c r="C6" s="16"/>
+      <c r="D6" s="16"/>
+      <c r="E6" s="16"/>
+      <c r="F6" s="16"/>
+      <c r="G6" s="16"/>
+      <c r="H6" s="16"/>
     </row>
     <row r="7" spans="1:8" ht="28.05" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A7" s="16" t="s">
+      <c r="A7" s="18" t="s">
         <v>14</v>
       </c>
-      <c r="B7" s="15"/>
-      <c r="C7" s="15"/>
-      <c r="D7" s="15"/>
-      <c r="E7" s="15"/>
-      <c r="F7" s="15"/>
-      <c r="G7" s="15"/>
-      <c r="H7" s="15"/>
+      <c r="B7" s="16"/>
+      <c r="C7" s="16"/>
+      <c r="D7" s="16"/>
+      <c r="E7" s="16"/>
+      <c r="F7" s="16"/>
+      <c r="G7" s="16"/>
+      <c r="H7" s="16"/>
     </row>
     <row r="8" spans="1:8" ht="32" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A8" s="7" t="s">
@@ -1268,16 +1272,16 @@
       </c>
     </row>
     <row r="15" spans="1:8" ht="28.05" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A15" s="16" t="s">
+      <c r="A15" s="18" t="s">
         <v>42</v>
       </c>
-      <c r="B15" s="15"/>
-      <c r="C15" s="15"/>
-      <c r="D15" s="15"/>
-      <c r="E15" s="15"/>
-      <c r="F15" s="15"/>
-      <c r="G15" s="15"/>
-      <c r="H15" s="15"/>
+      <c r="B15" s="16"/>
+      <c r="C15" s="16"/>
+      <c r="D15" s="16"/>
+      <c r="E15" s="16"/>
+      <c r="F15" s="16"/>
+      <c r="G15" s="16"/>
+      <c r="H15" s="16"/>
     </row>
     <row r="16" spans="1:8" ht="32" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A16" s="7" t="s">
@@ -1566,16 +1570,16 @@
       </c>
     </row>
     <row r="28" spans="1:8" ht="28.05" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A28" s="16" t="s">
+      <c r="A28" s="18" t="s">
         <v>116</v>
       </c>
-      <c r="B28" s="15"/>
-      <c r="C28" s="15"/>
-      <c r="D28" s="15"/>
-      <c r="E28" s="15"/>
-      <c r="F28" s="15"/>
-      <c r="G28" s="15"/>
-      <c r="H28" s="15"/>
+      <c r="B28" s="16"/>
+      <c r="C28" s="16"/>
+      <c r="D28" s="16"/>
+      <c r="E28" s="16"/>
+      <c r="F28" s="16"/>
+      <c r="G28" s="16"/>
+      <c r="H28" s="16"/>
     </row>
     <row r="29" spans="1:8" ht="28.05" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A29" s="7" t="s">
@@ -1596,8 +1600,8 @@
       <c r="F29" s="7" t="s">
         <v>122</v>
       </c>
-      <c r="G29" s="15"/>
-      <c r="H29" s="15"/>
+      <c r="G29" s="16"/>
+      <c r="H29" s="16"/>
     </row>
     <row r="30" spans="1:8" ht="59.55" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A30" s="9" t="s">
@@ -1681,16 +1685,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="G29:H29"/>
+    <mergeCell ref="A28:H28"/>
+    <mergeCell ref="B5:H5"/>
+    <mergeCell ref="A15:H15"/>
+    <mergeCell ref="B6:H6"/>
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="B3:H3"/>
     <mergeCell ref="A7:H7"/>
     <mergeCell ref="B4:H4"/>
     <mergeCell ref="A2:H2"/>
-    <mergeCell ref="G29:H29"/>
-    <mergeCell ref="A28:H28"/>
-    <mergeCell ref="B5:H5"/>
-    <mergeCell ref="A15:H15"/>
-    <mergeCell ref="B6:H6"/>
   </mergeCells>
   <phoneticPr fontId="7" type="noConversion"/>
   <hyperlinks>
